--- a/data/trans_orig/IP31KM12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM12_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>122555</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>120863</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>111862</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>108301</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>113586</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>97,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>136396</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134645</t>
+          <t>112706</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>117854</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>248259</t>
+          <t>238637</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244764</t>
+          <t>234888</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250013</t>
+          <t>240521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2389</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5950</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>228322</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>223674</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>230226</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>180484</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>175181</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>183793</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>94,13%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>98,75%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>244284</t>
+          <t>174938</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239637</t>
+          <t>169723</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>246449</t>
+          <t>178193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>424768</t>
+          <t>403259</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>418718</t>
+          <t>396779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>428685</t>
+          <t>407244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2919</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7567</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5630</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2321</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10933</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,02%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4949</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>185813</t>
+          <t>165551</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>182150</t>
+          <t>161198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187582</t>
+          <t>166522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>182050</t>
+          <t>152443</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177859</t>
+          <t>148002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>154223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>367864</t>
+          <t>317995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>363298</t>
+          <t>313238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>370226</t>
+          <t>320513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5324</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2436</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6099</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8041</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>164138</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>159166</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>95,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>156525</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>150673</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>160544</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>95,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>91,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>175272</t>
+          <t>156081</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>171011</t>
+          <t>149671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>160053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>331797</t>
+          <t>320218</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>324684</t>
+          <t>313514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336033</t>
+          <t>324846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6999</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7994</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3975</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13846</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>14308</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>680565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>674888</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>684044</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>888</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>634685</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>626735</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>641562</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599545</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>731772</t>
+          <t>591684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>741486</t>
+          <t>605462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1372687</t>
+          <t>1280109</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1362794</t>
+          <t>1269948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1380432</t>
+          <t>1287702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6259</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>18449</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11572</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>26399</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>24922</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>35083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
